--- a/docs/CTRBLXAI_Weapons_Equipment.xlsx
+++ b/docs/CTRBLXAI_Weapons_Equipment.xlsx
@@ -598,12 +598,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Base RT + Effective Armor WT.</t>
+          <t>Modified Base RT = (unit's own Base RT + Effective Armor WT) × permanent trait base-RT modifiers × active Haste (×0.90) / Slow (×1.10) / Frozen (×2). Unit's own Base RT (Layer 1): player units 400; enemy units = their KIND base — Grunt 400 / Veteran 380 / Elite 350 (not a flat 400); boss units 300 (core_stats 'Boss unit'). Effective Armor WT = non-weapon equipment WT (Body/Head/Gloves/Feet/Accessory) after STR burden reduction; Armor Off-Hand WT is excluded (project_rules 'Armor Off-Hand WT'). Every Base-RT-derived per-turn cost (Move, Basic Attack, Guard, Interact, Item, Push, Rest) uses this value, so enemy kind base RT flows into every turn. It is also the input to the one-time Starting RT reduction (core_stats 'Starting RT applies to ALL units').</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>Locked</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>USER RULING 2026-10-04 (three-layer RT model, final): clarified the kind-base input and modifier order. Previous text was 'Base RT + Effective Armor WT.', which implied a flat 400 base for everyone. Weapon BP pricing references (Two-Attack Cycle RT, Attacks per 1000 CT) still assume a 400-base player unit.</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1109,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1H | 1 | Single | None | Piercing Edge (120)</t>
+          <t>1H | 1 | Single | None | Piercing Edge (120): target effective Defense x0.80 on hit</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1124,12 +1129,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>52 / 80 / 45 / 0</t>
+          <t>44 / 80 / 80 / 0</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1H | 1-3 | Single | None | — (Range 3 melee)</t>
+          <t>1H | 1-3 | Single | None | — (Range 3 melee, RT Delay control identity)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1405,7 +1410,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1H | 2-4 | Single | Direct | Venomous (200)</t>
+          <t>1H | 2-4 | Single | Direct | Poisonous (200): applies Poison debuff on hit</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2773,7 +2778,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>On hit. Apply Poison status. Poison damage per turn = floor(Target Max HP × 0.04). Duration: 3 turns. Reapplication refreshes duration. Poison ignores Defense and does not scale with attacker stats.</t>
+          <t>On hit, apply the Venom debuff (unlimited until cured; round(Max HP x 0.03 x Venom Strength x Debuff Resistance x Boss HP% Modifier)/tick; Venom Strength +1 per reapply; heals reduce Strength; Undead immune). Application only.</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -2969,12 +2974,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>38 / 35 / 54 / 9</t>
+          <t>50 / 30 / 45 / 9</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>1H | 1 | Single | None | Ignite (150): applies Burn DoT on hit</t>
+          <t>1H | 1 | Single | None | Ignite (150): applies Burn (25% of Fire damage) on hit; non-elemental hits execute as Fire</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -3407,12 +3412,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>5 / 68 / 94 / 0</t>
+          <t>38 / 68 / 55 / 0</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2H | 1-2 | Impact Splash(400) | Channeled(80) | — (zero damage, pure AOE RT Delay)</t>
+          <t>2H | 1-3 | Impact Splash(400) | Channeled(80) | — (AOE effect-carrier: real damage + RT Delay)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
